--- a/sgate-database.xlsx
+++ b/sgate-database.xlsx
@@ -15,6 +15,13 @@
     <sheet name="Kontainer" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="Log Notifikasi" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
+  <definedNames>
+    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">DO!$A$1:$H$30</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">EMKL!$A$1:$D$30</definedName>
+    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Kontainer!$A$1:$J$30</definedName>
+    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">'Log Notifikasi'!$A$1:$E$30</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Tarif!$A$1:$C$3</definedName>
+  </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -24,6 +31,50 @@
 </workbook>
 </file>
 
+<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tips: penulisan spasi &amp; huruf besar/kecil tidak masalah (aplikasi otomatis menyamakan 'MSKU 220118 9' dengan 'msku2201189'). Yang penting digit dan hurufnya identik dengan yang didaftarkan EMKL — beda satu karakter saja akan dianggap Mismatch.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Setiap kontainer yang sudah berstatus Valid/Mismatch tidak bisa dicocokkan ulang di gate. Kalau salah input, kontainer itu akan 'terpakai' sebagai Mismatch dan tidak muncul lagi di pilihan 'DO menunggu' — refresh halaman gate untuk reset data demo.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="68">
   <si>
@@ -237,7 +288,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="#,##0"/>
+    <numFmt numFmtId="165" formatCode="#,##0;\-#,##0;\-"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -302,21 +353,17 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
       <sz val="10"/>
-      <color rgb="FF0D2B26"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -335,6 +382,12 @@
         <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F5F3"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border diagonalUp="false" diagonalDown="false">
@@ -346,16 +399,16 @@
     </border>
     <border diagonalUp="false" diagonalDown="false">
       <left style="thin">
-        <color rgb="FFB7C7C2"/>
+        <color rgb="FFD8E2DF"/>
       </left>
       <right style="thin">
-        <color rgb="FFB7C7C2"/>
+        <color rgb="FFD8E2DF"/>
       </right>
       <top style="thin">
-        <color rgb="FFB7C7C2"/>
+        <color rgb="FFD8E2DF"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB7C7C2"/>
+        <color rgb="FFD8E2DF"/>
       </bottom>
       <diagonal/>
     </border>
@@ -385,16 +438,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -402,16 +459,16 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -419,19 +476,23 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -443,6 +504,47 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="5">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF073D30"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF1F5F3"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -459,16 +561,16 @@
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFB7C7C2"/>
+      <rgbColor rgb="FFC0C0C0"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFF1F5F3"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FFD8E2DF"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -504,6 +606,26 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -689,139 +811,139 @@
   <dimension ref="B2:C21"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="100"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="100"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="2" t="s">
+    <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="2"/>
-      <c r="C5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="4" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="2"/>
-      <c r="C12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="3"/>
+      <c r="C13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="4" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="2"/>
-      <c r="C17" s="3"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="4"/>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="4" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="4" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="4" t="s">
         <v>28</v>
       </c>
     </row>
@@ -844,44 +966,45 @@
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="20"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="7" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="8" t="n">
+      <c r="B2" s="9" t="n">
         <v>350000</v>
       </c>
-      <c r="C2" s="8" t="n">
+      <c r="C2" s="9" t="n">
         <v>150000</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="8" t="n">
+      <c r="B3" s="9" t="n">
         <v>500000</v>
       </c>
-      <c r="C3" s="8" t="n">
+      <c r="C3" s="9" t="n">
         <v>200000</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C3"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -889,6 +1012,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -897,44 +1021,213 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="16"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="7" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="9" t="n">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="10" t="s">
         <v>40</v>
       </c>
     </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="12"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="11"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="12"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="11"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="12"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="11"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="12"/>
+      <c r="B10" s="12"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="12"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="12"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="12"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="11"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="12"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="11"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="12"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="11"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="12"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="11"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="12"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="11"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="12"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="11"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="12"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="11"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="12"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:D30"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -942,6 +1235,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -953,463 +1247,604 @@
   <dimension ref="A1:H30"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="16"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
+    <row r="1" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="7" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="9" t="n">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="F2" s="10" t="n">
+      <c r="F2" s="9" t="n">
         <f aca="false">SUMIFS(Kontainer!I:I,Kontainer!B:B,B2)</f>
         <v>500000</v>
       </c>
-      <c r="G2" s="10" t="n">
+      <c r="G2" s="9" t="n">
         <f aca="false">SUMIFS(Kontainer!J:J,Kontainer!B:B,B2)</f>
         <v>200000</v>
       </c>
-      <c r="H2" s="11" t="n">
+      <c r="H2" s="9" t="n">
         <f aca="false">F2+G2</f>
         <v>700000</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F3" s="10" t="n">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="13" t="n">
         <f aca="false">SUMIFS(Kontainer!I:I,Kontainer!B:B,B3)</f>
         <v>0</v>
       </c>
-      <c r="G3" s="10" t="n">
+      <c r="G3" s="13" t="n">
         <f aca="false">SUMIFS(Kontainer!J:J,Kontainer!B:B,B3)</f>
         <v>0</v>
       </c>
-      <c r="H3" s="11" t="n">
+      <c r="H3" s="13" t="n">
         <f aca="false">F3+G3</f>
         <v>0</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F4" s="10" t="n">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="12"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="9" t="n">
         <f aca="false">SUMIFS(Kontainer!I:I,Kontainer!B:B,B4)</f>
         <v>0</v>
       </c>
-      <c r="G4" s="10" t="n">
+      <c r="G4" s="9" t="n">
         <f aca="false">SUMIFS(Kontainer!J:J,Kontainer!B:B,B4)</f>
         <v>0</v>
       </c>
-      <c r="H4" s="11" t="n">
+      <c r="H4" s="9" t="n">
         <f aca="false">F4+G4</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F5" s="10" t="n">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="11"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="13" t="n">
         <f aca="false">SUMIFS(Kontainer!I:I,Kontainer!B:B,B5)</f>
         <v>0</v>
       </c>
-      <c r="G5" s="10" t="n">
+      <c r="G5" s="13" t="n">
         <f aca="false">SUMIFS(Kontainer!J:J,Kontainer!B:B,B5)</f>
         <v>0</v>
       </c>
-      <c r="H5" s="11" t="n">
+      <c r="H5" s="13" t="n">
         <f aca="false">F5+G5</f>
         <v>0</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F6" s="10" t="n">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="12"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="9" t="n">
         <f aca="false">SUMIFS(Kontainer!I:I,Kontainer!B:B,B6)</f>
         <v>0</v>
       </c>
-      <c r="G6" s="10" t="n">
+      <c r="G6" s="9" t="n">
         <f aca="false">SUMIFS(Kontainer!J:J,Kontainer!B:B,B6)</f>
         <v>0</v>
       </c>
-      <c r="H6" s="11" t="n">
+      <c r="H6" s="9" t="n">
         <f aca="false">F6+G6</f>
         <v>0</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F7" s="10" t="n">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="11"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="13" t="n">
         <f aca="false">SUMIFS(Kontainer!I:I,Kontainer!B:B,B7)</f>
         <v>0</v>
       </c>
-      <c r="G7" s="10" t="n">
+      <c r="G7" s="13" t="n">
         <f aca="false">SUMIFS(Kontainer!J:J,Kontainer!B:B,B7)</f>
         <v>0</v>
       </c>
-      <c r="H7" s="11" t="n">
+      <c r="H7" s="13" t="n">
         <f aca="false">F7+G7</f>
         <v>0</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F8" s="10" t="n">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="12"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="9" t="n">
         <f aca="false">SUMIFS(Kontainer!I:I,Kontainer!B:B,B8)</f>
         <v>0</v>
       </c>
-      <c r="G8" s="10" t="n">
+      <c r="G8" s="9" t="n">
         <f aca="false">SUMIFS(Kontainer!J:J,Kontainer!B:B,B8)</f>
         <v>0</v>
       </c>
-      <c r="H8" s="11" t="n">
+      <c r="H8" s="9" t="n">
         <f aca="false">F8+G8</f>
         <v>0</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F9" s="10" t="n">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="11"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="13" t="n">
         <f aca="false">SUMIFS(Kontainer!I:I,Kontainer!B:B,B9)</f>
         <v>0</v>
       </c>
-      <c r="G9" s="10" t="n">
+      <c r="G9" s="13" t="n">
         <f aca="false">SUMIFS(Kontainer!J:J,Kontainer!B:B,B9)</f>
         <v>0</v>
       </c>
-      <c r="H9" s="11" t="n">
+      <c r="H9" s="13" t="n">
         <f aca="false">F9+G9</f>
         <v>0</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F10" s="10" t="n">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="12"/>
+      <c r="B10" s="12"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="9" t="n">
         <f aca="false">SUMIFS(Kontainer!I:I,Kontainer!B:B,B10)</f>
         <v>0</v>
       </c>
-      <c r="G10" s="10" t="n">
+      <c r="G10" s="9" t="n">
         <f aca="false">SUMIFS(Kontainer!J:J,Kontainer!B:B,B10)</f>
         <v>0</v>
       </c>
-      <c r="H10" s="11" t="n">
+      <c r="H10" s="9" t="n">
         <f aca="false">F10+G10</f>
         <v>0</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F11" s="10" t="n">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="13" t="n">
         <f aca="false">SUMIFS(Kontainer!I:I,Kontainer!B:B,B11)</f>
         <v>0</v>
       </c>
-      <c r="G11" s="10" t="n">
+      <c r="G11" s="13" t="n">
         <f aca="false">SUMIFS(Kontainer!J:J,Kontainer!B:B,B11)</f>
         <v>0</v>
       </c>
-      <c r="H11" s="11" t="n">
+      <c r="H11" s="13" t="n">
         <f aca="false">F11+G11</f>
         <v>0</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F12" s="10" t="n">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="12"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="9" t="n">
         <f aca="false">SUMIFS(Kontainer!I:I,Kontainer!B:B,B12)</f>
         <v>0</v>
       </c>
-      <c r="G12" s="10" t="n">
+      <c r="G12" s="9" t="n">
         <f aca="false">SUMIFS(Kontainer!J:J,Kontainer!B:B,B12)</f>
         <v>0</v>
       </c>
-      <c r="H12" s="11" t="n">
+      <c r="H12" s="9" t="n">
         <f aca="false">F12+G12</f>
         <v>0</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F13" s="10" t="n">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="13" t="n">
         <f aca="false">SUMIFS(Kontainer!I:I,Kontainer!B:B,B13)</f>
         <v>0</v>
       </c>
-      <c r="G13" s="10" t="n">
+      <c r="G13" s="13" t="n">
         <f aca="false">SUMIFS(Kontainer!J:J,Kontainer!B:B,B13)</f>
         <v>0</v>
       </c>
-      <c r="H13" s="11" t="n">
+      <c r="H13" s="13" t="n">
         <f aca="false">F13+G13</f>
         <v>0</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F14" s="10" t="n">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="12"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="9" t="n">
         <f aca="false">SUMIFS(Kontainer!I:I,Kontainer!B:B,B14)</f>
         <v>0</v>
       </c>
-      <c r="G14" s="10" t="n">
+      <c r="G14" s="9" t="n">
         <f aca="false">SUMIFS(Kontainer!J:J,Kontainer!B:B,B14)</f>
         <v>0</v>
       </c>
-      <c r="H14" s="11" t="n">
+      <c r="H14" s="9" t="n">
         <f aca="false">F14+G14</f>
         <v>0</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F15" s="10" t="n">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="13" t="n">
         <f aca="false">SUMIFS(Kontainer!I:I,Kontainer!B:B,B15)</f>
         <v>0</v>
       </c>
-      <c r="G15" s="10" t="n">
+      <c r="G15" s="13" t="n">
         <f aca="false">SUMIFS(Kontainer!J:J,Kontainer!B:B,B15)</f>
         <v>0</v>
       </c>
-      <c r="H15" s="11" t="n">
+      <c r="H15" s="13" t="n">
         <f aca="false">F15+G15</f>
         <v>0</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F16" s="10" t="n">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="12"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="9" t="n">
         <f aca="false">SUMIFS(Kontainer!I:I,Kontainer!B:B,B16)</f>
         <v>0</v>
       </c>
-      <c r="G16" s="10" t="n">
+      <c r="G16" s="9" t="n">
         <f aca="false">SUMIFS(Kontainer!J:J,Kontainer!B:B,B16)</f>
         <v>0</v>
       </c>
-      <c r="H16" s="11" t="n">
+      <c r="H16" s="9" t="n">
         <f aca="false">F16+G16</f>
         <v>0</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F17" s="10" t="n">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="11"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="13" t="n">
         <f aca="false">SUMIFS(Kontainer!I:I,Kontainer!B:B,B17)</f>
         <v>0</v>
       </c>
-      <c r="G17" s="10" t="n">
+      <c r="G17" s="13" t="n">
         <f aca="false">SUMIFS(Kontainer!J:J,Kontainer!B:B,B17)</f>
         <v>0</v>
       </c>
-      <c r="H17" s="11" t="n">
+      <c r="H17" s="13" t="n">
         <f aca="false">F17+G17</f>
         <v>0</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F18" s="10" t="n">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="12"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="9" t="n">
         <f aca="false">SUMIFS(Kontainer!I:I,Kontainer!B:B,B18)</f>
         <v>0</v>
       </c>
-      <c r="G18" s="10" t="n">
+      <c r="G18" s="9" t="n">
         <f aca="false">SUMIFS(Kontainer!J:J,Kontainer!B:B,B18)</f>
         <v>0</v>
       </c>
-      <c r="H18" s="11" t="n">
+      <c r="H18" s="9" t="n">
         <f aca="false">F18+G18</f>
         <v>0</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F19" s="10" t="n">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="11"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="13" t="n">
         <f aca="false">SUMIFS(Kontainer!I:I,Kontainer!B:B,B19)</f>
         <v>0</v>
       </c>
-      <c r="G19" s="10" t="n">
+      <c r="G19" s="13" t="n">
         <f aca="false">SUMIFS(Kontainer!J:J,Kontainer!B:B,B19)</f>
         <v>0</v>
       </c>
-      <c r="H19" s="11" t="n">
+      <c r="H19" s="13" t="n">
         <f aca="false">F19+G19</f>
         <v>0</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F20" s="10" t="n">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="12"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="9" t="n">
         <f aca="false">SUMIFS(Kontainer!I:I,Kontainer!B:B,B20)</f>
         <v>0</v>
       </c>
-      <c r="G20" s="10" t="n">
+      <c r="G20" s="9" t="n">
         <f aca="false">SUMIFS(Kontainer!J:J,Kontainer!B:B,B20)</f>
         <v>0</v>
       </c>
-      <c r="H20" s="11" t="n">
+      <c r="H20" s="9" t="n">
         <f aca="false">F20+G20</f>
         <v>0</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F21" s="10" t="n">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="11"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="13" t="n">
         <f aca="false">SUMIFS(Kontainer!I:I,Kontainer!B:B,B21)</f>
         <v>0</v>
       </c>
-      <c r="G21" s="10" t="n">
+      <c r="G21" s="13" t="n">
         <f aca="false">SUMIFS(Kontainer!J:J,Kontainer!B:B,B21)</f>
         <v>0</v>
       </c>
-      <c r="H21" s="11" t="n">
+      <c r="H21" s="13" t="n">
         <f aca="false">F21+G21</f>
         <v>0</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F22" s="10" t="n">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="12"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="9" t="n">
         <f aca="false">SUMIFS(Kontainer!I:I,Kontainer!B:B,B22)</f>
         <v>0</v>
       </c>
-      <c r="G22" s="10" t="n">
+      <c r="G22" s="9" t="n">
         <f aca="false">SUMIFS(Kontainer!J:J,Kontainer!B:B,B22)</f>
         <v>0</v>
       </c>
-      <c r="H22" s="11" t="n">
+      <c r="H22" s="9" t="n">
         <f aca="false">F22+G22</f>
         <v>0</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F23" s="10" t="n">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="11"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="13" t="n">
         <f aca="false">SUMIFS(Kontainer!I:I,Kontainer!B:B,B23)</f>
         <v>0</v>
       </c>
-      <c r="G23" s="10" t="n">
+      <c r="G23" s="13" t="n">
         <f aca="false">SUMIFS(Kontainer!J:J,Kontainer!B:B,B23)</f>
         <v>0</v>
       </c>
-      <c r="H23" s="11" t="n">
+      <c r="H23" s="13" t="n">
         <f aca="false">F23+G23</f>
         <v>0</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F24" s="10" t="n">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="12"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="9" t="n">
         <f aca="false">SUMIFS(Kontainer!I:I,Kontainer!B:B,B24)</f>
         <v>0</v>
       </c>
-      <c r="G24" s="10" t="n">
+      <c r="G24" s="9" t="n">
         <f aca="false">SUMIFS(Kontainer!J:J,Kontainer!B:B,B24)</f>
         <v>0</v>
       </c>
-      <c r="H24" s="11" t="n">
+      <c r="H24" s="9" t="n">
         <f aca="false">F24+G24</f>
         <v>0</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F25" s="10" t="n">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="11"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="13" t="n">
         <f aca="false">SUMIFS(Kontainer!I:I,Kontainer!B:B,B25)</f>
         <v>0</v>
       </c>
-      <c r="G25" s="10" t="n">
+      <c r="G25" s="13" t="n">
         <f aca="false">SUMIFS(Kontainer!J:J,Kontainer!B:B,B25)</f>
         <v>0</v>
       </c>
-      <c r="H25" s="11" t="n">
+      <c r="H25" s="13" t="n">
         <f aca="false">F25+G25</f>
         <v>0</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F26" s="10" t="n">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="12"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="9" t="n">
         <f aca="false">SUMIFS(Kontainer!I:I,Kontainer!B:B,B26)</f>
         <v>0</v>
       </c>
-      <c r="G26" s="10" t="n">
+      <c r="G26" s="9" t="n">
         <f aca="false">SUMIFS(Kontainer!J:J,Kontainer!B:B,B26)</f>
         <v>0</v>
       </c>
-      <c r="H26" s="11" t="n">
+      <c r="H26" s="9" t="n">
         <f aca="false">F26+G26</f>
         <v>0</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F27" s="10" t="n">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="11"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="13" t="n">
         <f aca="false">SUMIFS(Kontainer!I:I,Kontainer!B:B,B27)</f>
         <v>0</v>
       </c>
-      <c r="G27" s="10" t="n">
+      <c r="G27" s="13" t="n">
         <f aca="false">SUMIFS(Kontainer!J:J,Kontainer!B:B,B27)</f>
         <v>0</v>
       </c>
-      <c r="H27" s="11" t="n">
+      <c r="H27" s="13" t="n">
         <f aca="false">F27+G27</f>
         <v>0</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F28" s="10" t="n">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="12"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="9" t="n">
         <f aca="false">SUMIFS(Kontainer!I:I,Kontainer!B:B,B28)</f>
         <v>0</v>
       </c>
-      <c r="G28" s="10" t="n">
+      <c r="G28" s="9" t="n">
         <f aca="false">SUMIFS(Kontainer!J:J,Kontainer!B:B,B28)</f>
         <v>0</v>
       </c>
-      <c r="H28" s="11" t="n">
+      <c r="H28" s="9" t="n">
         <f aca="false">F28+G28</f>
         <v>0</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F29" s="10" t="n">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="11"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="13" t="n">
         <f aca="false">SUMIFS(Kontainer!I:I,Kontainer!B:B,B29)</f>
         <v>0</v>
       </c>
-      <c r="G29" s="10" t="n">
+      <c r="G29" s="13" t="n">
         <f aca="false">SUMIFS(Kontainer!J:J,Kontainer!B:B,B29)</f>
         <v>0</v>
       </c>
-      <c r="H29" s="11" t="n">
+      <c r="H29" s="13" t="n">
         <f aca="false">F29+G29</f>
         <v>0</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F30" s="10" t="n">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="12"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="9" t="n">
         <f aca="false">SUMIFS(Kontainer!I:I,Kontainer!B:B,B30)</f>
         <v>0</v>
       </c>
-      <c r="G30" s="10" t="n">
+      <c r="G30" s="9" t="n">
         <f aca="false">SUMIFS(Kontainer!J:J,Kontainer!B:B,B30)</f>
         <v>0</v>
       </c>
-      <c r="H30" s="11" t="n">
+      <c r="H30" s="9" t="n">
         <f aca="false">F30+G30</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H30"/>
   <dataValidations count="1">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E2:E500" type="list">
       <formula1>"Belum lunas,Lunas"</formula1>
@@ -1423,6 +1858,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1434,362 +1870,587 @@
   <dimension ref="A1:J30"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="16"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
+    <row r="1" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="9" t="n">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9" t="s">
+      <c r="G2" s="10"/>
+      <c r="H2" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="I2" s="10" t="n">
+      <c r="I2" s="9" t="n">
         <f aca="false">INDEX(Tarif!$B$2:$B$3,MATCH(D2,Tarif!$A$2:$A$3,0))</f>
         <v>500000</v>
       </c>
-      <c r="J2" s="10" t="n">
+      <c r="J2" s="9" t="n">
         <f aca="false">INDEX(Tarif!$C$2:$C$3,MATCH(D2,Tarif!$A$2:$A$3,0))</f>
         <v>200000</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I3" s="10" t="str">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="13" t="str">
         <f aca="false">IFERROR(INDEX(Tarif!$B$2:$B$3,MATCH(D3,Tarif!$A$2:$A$3,0)),"")</f>
         <v/>
       </c>
-      <c r="J3" s="10" t="str">
+      <c r="J3" s="13" t="str">
         <f aca="false">IFERROR(INDEX(Tarif!$C$2:$C$3,MATCH(D3,Tarif!$A$2:$A$3,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I4" s="10" t="str">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="12"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Tarif!$B$2:$B$3,MATCH(D4,Tarif!$A$2:$A$3,0)),"")</f>
         <v/>
       </c>
-      <c r="J4" s="10" t="str">
+      <c r="J4" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Tarif!$C$2:$C$3,MATCH(D4,Tarif!$A$2:$A$3,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I5" s="10" t="str">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="11"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="13" t="str">
         <f aca="false">IFERROR(INDEX(Tarif!$B$2:$B$3,MATCH(D5,Tarif!$A$2:$A$3,0)),"")</f>
         <v/>
       </c>
-      <c r="J5" s="10" t="str">
+      <c r="J5" s="13" t="str">
         <f aca="false">IFERROR(INDEX(Tarif!$C$2:$C$3,MATCH(D5,Tarif!$A$2:$A$3,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I6" s="10" t="str">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="12"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Tarif!$B$2:$B$3,MATCH(D6,Tarif!$A$2:$A$3,0)),"")</f>
         <v/>
       </c>
-      <c r="J6" s="10" t="str">
+      <c r="J6" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Tarif!$C$2:$C$3,MATCH(D6,Tarif!$A$2:$A$3,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I7" s="10" t="str">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="11"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="13" t="str">
         <f aca="false">IFERROR(INDEX(Tarif!$B$2:$B$3,MATCH(D7,Tarif!$A$2:$A$3,0)),"")</f>
         <v/>
       </c>
-      <c r="J7" s="10" t="str">
+      <c r="J7" s="13" t="str">
         <f aca="false">IFERROR(INDEX(Tarif!$C$2:$C$3,MATCH(D7,Tarif!$A$2:$A$3,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I8" s="10" t="str">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="12"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Tarif!$B$2:$B$3,MATCH(D8,Tarif!$A$2:$A$3,0)),"")</f>
         <v/>
       </c>
-      <c r="J8" s="10" t="str">
+      <c r="J8" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Tarif!$C$2:$C$3,MATCH(D8,Tarif!$A$2:$A$3,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I9" s="10" t="str">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="11"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="13" t="str">
         <f aca="false">IFERROR(INDEX(Tarif!$B$2:$B$3,MATCH(D9,Tarif!$A$2:$A$3,0)),"")</f>
         <v/>
       </c>
-      <c r="J9" s="10" t="str">
+      <c r="J9" s="13" t="str">
         <f aca="false">IFERROR(INDEX(Tarif!$C$2:$C$3,MATCH(D9,Tarif!$A$2:$A$3,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I10" s="10" t="str">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="12"/>
+      <c r="B10" s="12"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Tarif!$B$2:$B$3,MATCH(D10,Tarif!$A$2:$A$3,0)),"")</f>
         <v/>
       </c>
-      <c r="J10" s="10" t="str">
+      <c r="J10" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Tarif!$C$2:$C$3,MATCH(D10,Tarif!$A$2:$A$3,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I11" s="10" t="str">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="13" t="str">
         <f aca="false">IFERROR(INDEX(Tarif!$B$2:$B$3,MATCH(D11,Tarif!$A$2:$A$3,0)),"")</f>
         <v/>
       </c>
-      <c r="J11" s="10" t="str">
+      <c r="J11" s="13" t="str">
         <f aca="false">IFERROR(INDEX(Tarif!$C$2:$C$3,MATCH(D11,Tarif!$A$2:$A$3,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I12" s="10" t="str">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="12"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Tarif!$B$2:$B$3,MATCH(D12,Tarif!$A$2:$A$3,0)),"")</f>
         <v/>
       </c>
-      <c r="J12" s="10" t="str">
+      <c r="J12" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Tarif!$C$2:$C$3,MATCH(D12,Tarif!$A$2:$A$3,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I13" s="10" t="str">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="13" t="str">
         <f aca="false">IFERROR(INDEX(Tarif!$B$2:$B$3,MATCH(D13,Tarif!$A$2:$A$3,0)),"")</f>
         <v/>
       </c>
-      <c r="J13" s="10" t="str">
+      <c r="J13" s="13" t="str">
         <f aca="false">IFERROR(INDEX(Tarif!$C$2:$C$3,MATCH(D13,Tarif!$A$2:$A$3,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I14" s="10" t="str">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="12"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Tarif!$B$2:$B$3,MATCH(D14,Tarif!$A$2:$A$3,0)),"")</f>
         <v/>
       </c>
-      <c r="J14" s="10" t="str">
+      <c r="J14" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Tarif!$C$2:$C$3,MATCH(D14,Tarif!$A$2:$A$3,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I15" s="10" t="str">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="13" t="str">
         <f aca="false">IFERROR(INDEX(Tarif!$B$2:$B$3,MATCH(D15,Tarif!$A$2:$A$3,0)),"")</f>
         <v/>
       </c>
-      <c r="J15" s="10" t="str">
+      <c r="J15" s="13" t="str">
         <f aca="false">IFERROR(INDEX(Tarif!$C$2:$C$3,MATCH(D15,Tarif!$A$2:$A$3,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I16" s="10" t="str">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="12"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Tarif!$B$2:$B$3,MATCH(D16,Tarif!$A$2:$A$3,0)),"")</f>
         <v/>
       </c>
-      <c r="J16" s="10" t="str">
+      <c r="J16" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Tarif!$C$2:$C$3,MATCH(D16,Tarif!$A$2:$A$3,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I17" s="10" t="str">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="11"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="13" t="str">
         <f aca="false">IFERROR(INDEX(Tarif!$B$2:$B$3,MATCH(D17,Tarif!$A$2:$A$3,0)),"")</f>
         <v/>
       </c>
-      <c r="J17" s="10" t="str">
+      <c r="J17" s="13" t="str">
         <f aca="false">IFERROR(INDEX(Tarif!$C$2:$C$3,MATCH(D17,Tarif!$A$2:$A$3,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I18" s="10" t="str">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="12"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Tarif!$B$2:$B$3,MATCH(D18,Tarif!$A$2:$A$3,0)),"")</f>
         <v/>
       </c>
-      <c r="J18" s="10" t="str">
+      <c r="J18" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Tarif!$C$2:$C$3,MATCH(D18,Tarif!$A$2:$A$3,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I19" s="10" t="str">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="11"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="13" t="str">
         <f aca="false">IFERROR(INDEX(Tarif!$B$2:$B$3,MATCH(D19,Tarif!$A$2:$A$3,0)),"")</f>
         <v/>
       </c>
-      <c r="J19" s="10" t="str">
+      <c r="J19" s="13" t="str">
         <f aca="false">IFERROR(INDEX(Tarif!$C$2:$C$3,MATCH(D19,Tarif!$A$2:$A$3,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I20" s="10" t="str">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="12"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Tarif!$B$2:$B$3,MATCH(D20,Tarif!$A$2:$A$3,0)),"")</f>
         <v/>
       </c>
-      <c r="J20" s="10" t="str">
+      <c r="J20" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Tarif!$C$2:$C$3,MATCH(D20,Tarif!$A$2:$A$3,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I21" s="10" t="str">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="11"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="13" t="str">
         <f aca="false">IFERROR(INDEX(Tarif!$B$2:$B$3,MATCH(D21,Tarif!$A$2:$A$3,0)),"")</f>
         <v/>
       </c>
-      <c r="J21" s="10" t="str">
+      <c r="J21" s="13" t="str">
         <f aca="false">IFERROR(INDEX(Tarif!$C$2:$C$3,MATCH(D21,Tarif!$A$2:$A$3,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I22" s="10" t="str">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="12"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
+      <c r="I22" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Tarif!$B$2:$B$3,MATCH(D22,Tarif!$A$2:$A$3,0)),"")</f>
         <v/>
       </c>
-      <c r="J22" s="10" t="str">
+      <c r="J22" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Tarif!$C$2:$C$3,MATCH(D22,Tarif!$A$2:$A$3,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I23" s="10" t="str">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="11"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="13" t="str">
         <f aca="false">IFERROR(INDEX(Tarif!$B$2:$B$3,MATCH(D23,Tarif!$A$2:$A$3,0)),"")</f>
         <v/>
       </c>
-      <c r="J23" s="10" t="str">
+      <c r="J23" s="13" t="str">
         <f aca="false">IFERROR(INDEX(Tarif!$C$2:$C$3,MATCH(D23,Tarif!$A$2:$A$3,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I24" s="10" t="str">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="12"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Tarif!$B$2:$B$3,MATCH(D24,Tarif!$A$2:$A$3,0)),"")</f>
         <v/>
       </c>
-      <c r="J24" s="10" t="str">
+      <c r="J24" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Tarif!$C$2:$C$3,MATCH(D24,Tarif!$A$2:$A$3,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I25" s="10" t="str">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="11"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="13" t="str">
         <f aca="false">IFERROR(INDEX(Tarif!$B$2:$B$3,MATCH(D25,Tarif!$A$2:$A$3,0)),"")</f>
         <v/>
       </c>
-      <c r="J25" s="10" t="str">
+      <c r="J25" s="13" t="str">
         <f aca="false">IFERROR(INDEX(Tarif!$C$2:$C$3,MATCH(D25,Tarif!$A$2:$A$3,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I26" s="10" t="str">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="12"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
+      <c r="I26" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Tarif!$B$2:$B$3,MATCH(D26,Tarif!$A$2:$A$3,0)),"")</f>
         <v/>
       </c>
-      <c r="J26" s="10" t="str">
+      <c r="J26" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Tarif!$C$2:$C$3,MATCH(D26,Tarif!$A$2:$A$3,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I27" s="10" t="str">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="11"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="13" t="str">
         <f aca="false">IFERROR(INDEX(Tarif!$B$2:$B$3,MATCH(D27,Tarif!$A$2:$A$3,0)),"")</f>
         <v/>
       </c>
-      <c r="J27" s="10" t="str">
+      <c r="J27" s="13" t="str">
         <f aca="false">IFERROR(INDEX(Tarif!$C$2:$C$3,MATCH(D27,Tarif!$A$2:$A$3,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I28" s="10" t="str">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="12"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="12"/>
+      <c r="H28" s="12"/>
+      <c r="I28" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Tarif!$B$2:$B$3,MATCH(D28,Tarif!$A$2:$A$3,0)),"")</f>
         <v/>
       </c>
-      <c r="J28" s="10" t="str">
+      <c r="J28" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Tarif!$C$2:$C$3,MATCH(D28,Tarif!$A$2:$A$3,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I29" s="10" t="str">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="11"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="13" t="str">
         <f aca="false">IFERROR(INDEX(Tarif!$B$2:$B$3,MATCH(D29,Tarif!$A$2:$A$3,0)),"")</f>
         <v/>
       </c>
-      <c r="J29" s="10" t="str">
+      <c r="J29" s="13" t="str">
         <f aca="false">IFERROR(INDEX(Tarif!$C$2:$C$3,MATCH(D29,Tarif!$A$2:$A$3,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I30" s="10" t="str">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="12"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
+      <c r="I30" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Tarif!$B$2:$B$3,MATCH(D30,Tarif!$A$2:$A$3,0)),"")</f>
         <v/>
       </c>
-      <c r="J30" s="10" t="str">
+      <c r="J30" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Tarif!$C$2:$C$3,MATCH(D30,Tarif!$A$2:$A$3,0)),"")</f>
         <v/>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:J30"/>
   <dataValidations count="2">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D2:D500" type="list">
       <formula1>Tarif!$A$2:$A$3</formula1>
@@ -1807,6 +2468,8 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -1815,51 +2478,248 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="7" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="9" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="10" t="s">
         <v>46</v>
       </c>
     </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="12"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="11"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="12"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="11"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="12"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="11"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="12"/>
+      <c r="B10" s="12"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="12"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="12"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="12"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="11"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="12"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="11"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="12"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="11"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="12"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="11"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="12"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="11"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="12"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="11"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="12"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="11"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="12"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:E30"/>
   <dataValidations count="1">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B2:B500" type="list">
       <formula1>"Reminder,Mismatch,Valid,Pembayaran"</formula1>
@@ -1873,5 +2733,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>